--- a/artfynd/A 43123-2024 artfynd.xlsx
+++ b/artfynd/A 43123-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1059,7 +1059,7 @@
         <v>68198107</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,16 +1097,17 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743467.8179544678</v>
+        <v>743468</v>
       </c>
       <c r="R5" t="n">
-        <v>7174905.66030548</v>
+        <v>7174906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,19 +1137,14 @@
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack i stammen på en gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,7 +1174,7 @@
         <v>68199228</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
+        <v>57490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,16 +1212,17 @@
           <t>gammalt bo</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>743731.4002858398</v>
+        <v>743731</v>
       </c>
       <c r="R6" t="n">
-        <v>7174943.702653244</v>
+        <v>7174944</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,19 +1252,14 @@
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>bohål ca 2m ovan mark i stammen på en gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2246,7 +2238,7 @@
         <v>68197996</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
+        <v>57490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2284,16 +2276,17 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>743758.8731391679</v>
+        <v>743759</v>
       </c>
       <c r="R15" t="n">
-        <v>7175138.108500419</v>
+        <v>7175138</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2323,19 +2316,14 @@
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2544,7 +2532,7 @@
         <v>68199281</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
+        <v>57490</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2582,16 +2570,17 @@
           <t>gammalt bo</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>743516.790841297</v>
+        <v>743517</v>
       </c>
       <c r="R17" t="n">
-        <v>7175144.023388089</v>
+        <v>7175144</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2621,19 +2610,14 @@
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Bohål ca 2m ovan mark i stammen på gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2657,6 +2641,121 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123867019</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57506</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>743496</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7175226</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2017-10-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2017-10-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hack i 200 årig gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43123-2024 artfynd.xlsx
+++ b/artfynd/A 43123-2024 artfynd.xlsx
@@ -1059,7 +1059,7 @@
         <v>68198107</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>68199228</v>
       </c>
       <c r="B6" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>68197996</v>
       </c>
       <c r="B15" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>68199281</v>
       </c>
       <c r="B17" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>123867019</v>
       </c>
       <c r="B18" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
